--- a/data/SEIF.MI.xlsx
+++ b/data/SEIF.MI.xlsx
@@ -44049,6 +44049,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1900">
+      <c r="A1900" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B1900" t="n">
+        <v>8000</v>
+      </c>
+      <c r="C1900" t="n">
+        <v>0.244000002741814</v>
+      </c>
+      <c r="D1900" t="n">
+        <v>0.233999997377396</v>
+      </c>
+      <c r="E1900" t="n">
+        <v>0.244000002741814</v>
+      </c>
+      <c r="F1900" t="n">
+        <v>0.241999998688698</v>
+      </c>
+      <c r="G1900" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SEIF.MI.xlsx
+++ b/data/SEIF.MI.xlsx
@@ -44072,6 +44072,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1901">
+      <c r="A1901" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B1901" t="n">
+        <v>2000</v>
+      </c>
+      <c r="C1901" t="n">
+        <v>0.241999998688698</v>
+      </c>
+      <c r="D1901" t="n">
+        <v>0.241999998688698</v>
+      </c>
+      <c r="E1901" t="n">
+        <v>0.241999998688698</v>
+      </c>
+      <c r="F1901" t="n">
+        <v>0.241999998688698</v>
+      </c>
+      <c r="G1901" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SEIF.MI.xlsx
+++ b/data/SEIF.MI.xlsx
@@ -44095,6 +44095,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1902">
+      <c r="A1902" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B1902" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1902" t="n">
+        <v>0.241999998688698</v>
+      </c>
+      <c r="D1902" t="n">
+        <v>0.241999998688698</v>
+      </c>
+      <c r="E1902" t="n">
+        <v>0.241999998688698</v>
+      </c>
+      <c r="F1902" t="n">
+        <v>0.241999998688698</v>
+      </c>
+      <c r="G1902" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SEIF.MI.xlsx
+++ b/data/SEIF.MI.xlsx
@@ -43959,22 +43959,22 @@
     </row>
     <row r="1896">
       <c r="A1896" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B1896" t="n">
-        <v>2000</v>
+        <v>38000</v>
       </c>
       <c r="C1896" t="n">
-        <v>0.244000002741814</v>
+        <v>0.241999998688698</v>
       </c>
       <c r="D1896" t="n">
-        <v>0.244000002741814</v>
+        <v>0.238000005483627</v>
       </c>
       <c r="E1896" t="n">
-        <v>0.244000002741814</v>
+        <v>0.238000005483627</v>
       </c>
       <c r="F1896" t="n">
-        <v>0.244000002741814</v>
+        <v>0.241999998688698</v>
       </c>
       <c r="G1896" t="s">
         <v>7</v>
@@ -43982,22 +43982,22 @@
     </row>
     <row r="1897">
       <c r="A1897" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B1897" t="n">
-        <v>38000</v>
+        <v>2000</v>
       </c>
       <c r="C1897" t="n">
         <v>0.244000002741814</v>
       </c>
       <c r="D1897" t="n">
-        <v>0.236000001430511</v>
+        <v>0.244000002741814</v>
       </c>
       <c r="E1897" t="n">
         <v>0.244000002741814</v>
       </c>
       <c r="F1897" t="n">
-        <v>0.238000005483627</v>
+        <v>0.244000002741814</v>
       </c>
       <c r="G1897" t="s">
         <v>7</v>
@@ -44005,22 +44005,22 @@
     </row>
     <row r="1898">
       <c r="A1898" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B1898" t="n">
-        <v>16000</v>
+        <v>38000</v>
       </c>
       <c r="C1898" t="n">
         <v>0.244000002741814</v>
       </c>
       <c r="D1898" t="n">
-        <v>0.241999998688698</v>
+        <v>0.236000001430511</v>
       </c>
       <c r="E1898" t="n">
         <v>0.244000002741814</v>
       </c>
       <c r="F1898" t="n">
-        <v>0.244000002741814</v>
+        <v>0.238000005483627</v>
       </c>
       <c r="G1898" t="s">
         <v>7</v>
@@ -44028,22 +44028,22 @@
     </row>
     <row r="1899">
       <c r="A1899" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B1899" t="n">
-        <v>2000</v>
+        <v>16000</v>
       </c>
       <c r="C1899" t="n">
-        <v>0.241999998688698</v>
+        <v>0.244000002741814</v>
       </c>
       <c r="D1899" t="n">
         <v>0.241999998688698</v>
       </c>
       <c r="E1899" t="n">
-        <v>0.241999998688698</v>
+        <v>0.244000002741814</v>
       </c>
       <c r="F1899" t="n">
-        <v>0.241999998688698</v>
+        <v>0.244000002741814</v>
       </c>
       <c r="G1899" t="s">
         <v>7</v>
@@ -44051,19 +44051,19 @@
     </row>
     <row r="1900">
       <c r="A1900" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B1900" t="n">
-        <v>8000</v>
+        <v>2000</v>
       </c>
       <c r="C1900" t="n">
-        <v>0.244000002741814</v>
+        <v>0.241999998688698</v>
       </c>
       <c r="D1900" t="n">
-        <v>0.233999997377396</v>
+        <v>0.241999998688698</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.244000002741814</v>
+        <v>0.241999998688698</v>
       </c>
       <c r="F1900" t="n">
         <v>0.241999998688698</v>
@@ -44074,19 +44074,19 @@
     </row>
     <row r="1901">
       <c r="A1901" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B1901" t="n">
-        <v>2000</v>
+        <v>8000</v>
       </c>
       <c r="C1901" t="n">
-        <v>0.241999998688698</v>
+        <v>0.244000002741814</v>
       </c>
       <c r="D1901" t="n">
-        <v>0.241999998688698</v>
+        <v>0.233999997377396</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.241999998688698</v>
+        <v>0.244000002741814</v>
       </c>
       <c r="F1901" t="n">
         <v>0.241999998688698</v>
@@ -44097,10 +44097,10 @@
     </row>
     <row r="1902">
       <c r="A1902" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B1902" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="C1902" t="n">
         <v>0.241999998688698</v>
@@ -44115,6 +44115,29 @@
         <v>0.241999998688698</v>
       </c>
       <c r="G1902" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1903">
+      <c r="A1903" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B1903" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1903" t="n">
+        <v>0.241999998688698</v>
+      </c>
+      <c r="D1903" t="n">
+        <v>0.241999998688698</v>
+      </c>
+      <c r="E1903" t="n">
+        <v>0.241999998688698</v>
+      </c>
+      <c r="F1903" t="n">
+        <v>0.241999998688698</v>
+      </c>
+      <c r="G1903" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/SEIF.MI.xlsx
+++ b/data/SEIF.MI.xlsx
@@ -44141,6 +44141,52 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1904">
+      <c r="A1904" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B1904" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1904" t="n">
+        <v>0.241999998688698</v>
+      </c>
+      <c r="D1904" t="n">
+        <v>0.241999998688698</v>
+      </c>
+      <c r="E1904" t="n">
+        <v>0.241999998688698</v>
+      </c>
+      <c r="F1904" t="n">
+        <v>0.241999998688698</v>
+      </c>
+      <c r="G1904" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1905">
+      <c r="A1905" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B1905" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1905" t="n">
+        <v>0.241999998688698</v>
+      </c>
+      <c r="D1905" t="n">
+        <v>0.241999998688698</v>
+      </c>
+      <c r="E1905" t="n">
+        <v>0.241999998688698</v>
+      </c>
+      <c r="F1905" t="n">
+        <v>0.241999998688698</v>
+      </c>
+      <c r="G1905" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SEIF.MI.xlsx
+++ b/data/SEIF.MI.xlsx
@@ -49957,6 +49957,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1908">
+      <c r="A1908" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B1908" t="n">
+        <v>14000</v>
+      </c>
+      <c r="C1908" t="n">
+        <v>0.239999994635582</v>
+      </c>
+      <c r="D1908" t="n">
+        <v>0.233999997377396</v>
+      </c>
+      <c r="E1908" t="n">
+        <v>0.236000001430511</v>
+      </c>
+      <c r="F1908" t="n">
+        <v>0.239999994635582</v>
+      </c>
+      <c r="G1908" t="n">
+        <v>0.239999994635582</v>
+      </c>
+      <c r="H1908" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SEIF.MI.xlsx
+++ b/data/SEIF.MI.xlsx
@@ -44256,6 +44256,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1909">
+      <c r="A1909" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B1909" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1909" t="n">
+        <v>0.239999994635582</v>
+      </c>
+      <c r="D1909" t="n">
+        <v>0.239999994635582</v>
+      </c>
+      <c r="E1909" t="n">
+        <v>0.239999994635582</v>
+      </c>
+      <c r="F1909" t="n">
+        <v>0.239999994635582</v>
+      </c>
+      <c r="G1909" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SEIF.MI.xlsx
+++ b/data/SEIF.MI.xlsx
@@ -44279,6 +44279,50 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1910">
+      <c r="A1910" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B1910" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1910" t="n">
+        <v>0.239999994635582</v>
+      </c>
+      <c r="D1910" t="n">
+        <v>0.239999994635582</v>
+      </c>
+      <c r="E1910" t="n">
+        <v>0.239999994635582</v>
+      </c>
+      <c r="F1910" t="n">
+        <v>0.239999994635582</v>
+      </c>
+      <c r="G1910" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1911">
+      <c r="A1911" s="1" t="n">
+        <v>46293.2916666667</v>
+      </c>
+      <c r="B1911" t="n">
+        <v>2000</v>
+      </c>
+      <c r="C1911" t="n">
+        <v>0.23199999332428</v>
+      </c>
+      <c r="D1911" t="n">
+        <v>0.23199999332428</v>
+      </c>
+      <c r="E1911" t="n">
+        <v>0.23199999332428</v>
+      </c>
+      <c r="F1911"/>
+      <c r="G1911" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SEIF.MI.xlsx
+++ b/data/SEIF.MI.xlsx
@@ -44348,6 +44348,50 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1913">
+      <c r="A1913" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B1913" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1913" t="n">
+        <v>0.23199999332428</v>
+      </c>
+      <c r="D1913" t="n">
+        <v>0.23199999332428</v>
+      </c>
+      <c r="E1913" t="n">
+        <v>0.23199999332428</v>
+      </c>
+      <c r="F1913" t="n">
+        <v>0.23199999332428</v>
+      </c>
+      <c r="G1913" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1914">
+      <c r="A1914" s="1" t="n">
+        <v>46296.2916666667</v>
+      </c>
+      <c r="B1914" t="n">
+        <v>14000</v>
+      </c>
+      <c r="C1914" t="n">
+        <v>0.239999994635582</v>
+      </c>
+      <c r="D1914" t="n">
+        <v>0.238000005483627</v>
+      </c>
+      <c r="E1914" t="n">
+        <v>0.238000005483627</v>
+      </c>
+      <c r="F1914"/>
+      <c r="G1914" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SEIF.MI.xlsx
+++ b/data/SEIF.MI.xlsx
@@ -44387,7 +44387,9 @@
       <c r="E1914" t="n">
         <v>0.238000005483627</v>
       </c>
-      <c r="F1914"/>
+      <c r="F1914" t="n">
+        <v>0.239999994635582</v>
+      </c>
       <c r="G1914" t="s">
         <v>7</v>
       </c>

--- a/data/SEIF.MI.xlsx
+++ b/data/SEIF.MI.xlsx
@@ -44394,6 +44394,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1915">
+      <c r="A1915" s="1" t="n">
+        <v>46297.2916666667</v>
+      </c>
+      <c r="B1915" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1915" t="n">
+        <v>0.239999994635582</v>
+      </c>
+      <c r="D1915" t="n">
+        <v>0.239999994635582</v>
+      </c>
+      <c r="E1915" t="n">
+        <v>0.239999994635582</v>
+      </c>
+      <c r="F1915" t="n">
+        <v>0.239999994635582</v>
+      </c>
+      <c r="G1915" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SEIF.MI.xlsx
+++ b/data/SEIF.MI.xlsx
@@ -44417,6 +44417,50 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1916">
+      <c r="A1916" s="1" t="n">
+        <v>46300.2916666667</v>
+      </c>
+      <c r="B1916" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1916" t="n">
+        <v>0.239999994635582</v>
+      </c>
+      <c r="D1916" t="n">
+        <v>0.239999994635582</v>
+      </c>
+      <c r="E1916" t="n">
+        <v>0.239999994635582</v>
+      </c>
+      <c r="F1916" t="n">
+        <v>0.239999994635582</v>
+      </c>
+      <c r="G1916" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1917">
+      <c r="A1917" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B1917" t="n">
+        <v>16000</v>
+      </c>
+      <c r="C1917" t="n">
+        <v>0.238000005483627</v>
+      </c>
+      <c r="D1917" t="n">
+        <v>0.230000004172325</v>
+      </c>
+      <c r="E1917" t="n">
+        <v>0.230000004172325</v>
+      </c>
+      <c r="F1917"/>
+      <c r="G1917" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SEIF.MI.xlsx
+++ b/data/SEIF.MI.xlsx
@@ -44456,7 +44456,9 @@
       <c r="E1917" t="n">
         <v>0.230000004172325</v>
       </c>
-      <c r="F1917"/>
+      <c r="F1917" t="n">
+        <v>0.238000005483627</v>
+      </c>
       <c r="G1917" t="s">
         <v>7</v>
       </c>

--- a/data/SEIF.MI.xlsx
+++ b/data/SEIF.MI.xlsx
@@ -44463,6 +44463,50 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1918">
+      <c r="A1918" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B1918" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1918" t="n">
+        <v>0.238000005483627</v>
+      </c>
+      <c r="D1918" t="n">
+        <v>0.238000005483627</v>
+      </c>
+      <c r="E1918" t="n">
+        <v>0.238000005483627</v>
+      </c>
+      <c r="F1918" t="n">
+        <v>0.238000005483627</v>
+      </c>
+      <c r="G1918" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1919">
+      <c r="A1919" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B1919" t="n">
+        <v>8000</v>
+      </c>
+      <c r="C1919" t="n">
+        <v>0.222000002861023</v>
+      </c>
+      <c r="D1919" t="n">
+        <v>0.222000002861023</v>
+      </c>
+      <c r="E1919" t="n">
+        <v>0.222000002861023</v>
+      </c>
+      <c r="F1919"/>
+      <c r="G1919" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SEIF.MI.xlsx
+++ b/data/SEIF.MI.xlsx
@@ -44502,8 +44502,31 @@
       <c r="E1919" t="n">
         <v>0.222000002861023</v>
       </c>
-      <c r="F1919"/>
+      <c r="F1919" t="n">
+        <v>0.222000002861023</v>
+      </c>
       <c r="G1919" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1920">
+      <c r="A1920" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B1920" t="n">
+        <v>4000</v>
+      </c>
+      <c r="C1920" t="n">
+        <v>0.230000004172325</v>
+      </c>
+      <c r="D1920" t="n">
+        <v>0.230000004172325</v>
+      </c>
+      <c r="E1920" t="n">
+        <v>0.230000004172325</v>
+      </c>
+      <c r="F1920"/>
+      <c r="G1920" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/SEIF.MI.xlsx
+++ b/data/SEIF.MI.xlsx
@@ -44532,6 +44532,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1921">
+      <c r="A1921" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B1921" t="n">
+        <v>2000</v>
+      </c>
+      <c r="C1921" t="n">
+        <v>0.23199999332428</v>
+      </c>
+      <c r="D1921" t="n">
+        <v>0.23199999332428</v>
+      </c>
+      <c r="E1921" t="n">
+        <v>0.23199999332428</v>
+      </c>
+      <c r="F1921" t="n">
+        <v>0.23199999332428</v>
+      </c>
+      <c r="G1921" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SEIF.MI.xlsx
+++ b/data/SEIF.MI.xlsx
@@ -56203,6 +56203,64 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1926">
+      <c r="A1926" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1926" s="1" t="n">
+        <v>46314.2916666667</v>
+      </c>
+      <c r="C1926" t="n">
+        <v>0.228000000119209</v>
+      </c>
+      <c r="D1926" t="n">
+        <v>0.23199999332428</v>
+      </c>
+      <c r="E1926" t="n">
+        <v>0.224000006914139</v>
+      </c>
+      <c r="F1926" t="n">
+        <v>0.228000000119209</v>
+      </c>
+      <c r="G1926" t="n">
+        <v>0.228000000119209</v>
+      </c>
+      <c r="H1926" t="n">
+        <v>24000</v>
+      </c>
+      <c r="I1926" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1927">
+      <c r="A1927" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1927" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C1927" t="n">
+        <v>0.219999998807907</v>
+      </c>
+      <c r="D1927" t="n">
+        <v>0.225999996066093</v>
+      </c>
+      <c r="E1927" t="n">
+        <v>0.217999994754791</v>
+      </c>
+      <c r="F1927" t="n">
+        <v>0.224000006914139</v>
+      </c>
+      <c r="G1927" t="n">
+        <v>0.224000006914139</v>
+      </c>
+      <c r="H1927" t="n">
+        <v>38000</v>
+      </c>
+      <c r="I1927" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SEIF.MI.xlsx
+++ b/data/SEIF.MI.xlsx
@@ -56261,6 +56261,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1928">
+      <c r="A1928" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1928" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C1928" t="n">
+        <v>0.228000000119209</v>
+      </c>
+      <c r="D1928" t="n">
+        <v>0.228000000119209</v>
+      </c>
+      <c r="E1928" t="n">
+        <v>0.228000000119209</v>
+      </c>
+      <c r="F1928" t="n">
+        <v>0.228000000119209</v>
+      </c>
+      <c r="G1928" t="n">
+        <v>0.228000000119209</v>
+      </c>
+      <c r="H1928" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I1928" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SEIF.MI.xlsx
+++ b/data/SEIF.MI.xlsx
@@ -56290,6 +56290,64 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1929">
+      <c r="A1929" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1929" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C1929" t="n">
+        <v>0.228000000119209</v>
+      </c>
+      <c r="D1929" t="n">
+        <v>0.228000000119209</v>
+      </c>
+      <c r="E1929" t="n">
+        <v>0.228000000119209</v>
+      </c>
+      <c r="F1929" t="n">
+        <v>0.228000000119209</v>
+      </c>
+      <c r="G1929" t="n">
+        <v>0.228000000119209</v>
+      </c>
+      <c r="H1929" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1929" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1930">
+      <c r="A1930" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1930" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C1930" t="n">
+        <v>0.217999994754791</v>
+      </c>
+      <c r="D1930" t="n">
+        <v>0.219999998807907</v>
+      </c>
+      <c r="E1930" t="n">
+        <v>0.217999994754791</v>
+      </c>
+      <c r="F1930" t="n">
+        <v>0.219999998807907</v>
+      </c>
+      <c r="G1930" t="n">
+        <v>0.219999998807907</v>
+      </c>
+      <c r="H1930" t="n">
+        <v>14000</v>
+      </c>
+      <c r="I1930" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SEIF.MI.xlsx
+++ b/data/SEIF.MI.xlsx
@@ -56348,6 +56348,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1931">
+      <c r="A1931" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1931" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C1931" t="n">
+        <v>0.270000010728836</v>
+      </c>
+      <c r="D1931" t="n">
+        <v>0.270000010728836</v>
+      </c>
+      <c r="E1931" t="n">
+        <v>0.247999995946884</v>
+      </c>
+      <c r="F1931" t="n">
+        <v>0.259999990463257</v>
+      </c>
+      <c r="G1931" t="n">
+        <v>0.259999990463257</v>
+      </c>
+      <c r="H1931" t="n">
+        <v>814000</v>
+      </c>
+      <c r="I1931" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SEIF.MI.xlsx
+++ b/data/SEIF.MI.xlsx
@@ -56377,6 +56377,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1932">
+      <c r="A1932" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1932" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C1932" t="n">
+        <v>0.259999990463257</v>
+      </c>
+      <c r="D1932" t="n">
+        <v>0.28600001335144</v>
+      </c>
+      <c r="E1932" t="n">
+        <v>0.259999990463257</v>
+      </c>
+      <c r="F1932" t="n">
+        <v>0.261999994516373</v>
+      </c>
+      <c r="G1932" t="n">
+        <v>0.261999994516373</v>
+      </c>
+      <c r="H1932" t="n">
+        <v>824000</v>
+      </c>
+      <c r="I1932" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SEIF.MI.xlsx
+++ b/data/SEIF.MI.xlsx
@@ -56406,6 +56406,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1933">
+      <c r="A1933" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1933" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C1933" t="n">
+        <v>0.310000002384186</v>
+      </c>
+      <c r="D1933" t="n">
+        <v>0.319999992847443</v>
+      </c>
+      <c r="E1933" t="n">
+        <v>0.303999990224838</v>
+      </c>
+      <c r="F1933" t="n">
+        <v>0.300000011920929</v>
+      </c>
+      <c r="G1933" t="n">
+        <v>0.300000011920929</v>
+      </c>
+      <c r="H1933" t="n">
+        <v>574000</v>
+      </c>
+      <c r="I1933" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SEIF.MI.xlsx
+++ b/data/SEIF.MI.xlsx
@@ -56420,7 +56420,7 @@
         <v>0.319999992847443</v>
       </c>
       <c r="E1933" t="n">
-        <v>0.303999990224838</v>
+        <v>0.300000011920929</v>
       </c>
       <c r="F1933" t="n">
         <v>0.300000011920929</v>
@@ -56429,9 +56429,38 @@
         <v>0.300000011920929</v>
       </c>
       <c r="H1933" t="n">
-        <v>574000</v>
+        <v>590000</v>
       </c>
       <c r="I1933" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1934">
+      <c r="A1934" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1934" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C1934" t="n">
+        <v>0.291999995708466</v>
+      </c>
+      <c r="D1934" t="n">
+        <v>0.314000010490417</v>
+      </c>
+      <c r="E1934" t="n">
+        <v>0.280000001192093</v>
+      </c>
+      <c r="F1934" t="n">
+        <v>0.28999999165535</v>
+      </c>
+      <c r="G1934" t="n">
+        <v>0.28999999165535</v>
+      </c>
+      <c r="H1934" t="n">
+        <v>868000</v>
+      </c>
+      <c r="I1934" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SEIF.MI.xlsx
+++ b/data/SEIF.MI.xlsx
@@ -56464,6 +56464,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1935">
+      <c r="A1935" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1935" s="1" t="n">
+        <v>46325.3333333333</v>
+      </c>
+      <c r="C1935" t="n">
+        <v>0.28600001335144</v>
+      </c>
+      <c r="D1935" t="n">
+        <v>0.28600001335144</v>
+      </c>
+      <c r="E1935" t="n">
+        <v>0.26800000667572</v>
+      </c>
+      <c r="F1935" t="n">
+        <v>0.280000001192093</v>
+      </c>
+      <c r="G1935" t="n">
+        <v>0.280000001192093</v>
+      </c>
+      <c r="H1935" t="n">
+        <v>124000</v>
+      </c>
+      <c r="I1935" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
